--- a/web/files/港岛-半山-雅盈峰.xlsx
+++ b/web/files/港岛-半山-雅盈峰.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +121,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,7 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -898,7 +907,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -908,12 +917,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -923,12 +932,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -938,7 +947,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7372,27 +7381,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7496,34 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 -
@@ -7495,18 +7531,45 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$10323万
+$64,200/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+$7499万
+$59,800/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 -
@@ -7514,7 +7577,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 -
@@ -7522,60 +7585,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-$10323万
-$64,200/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-$7499万
-$59,800/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D10" s="21" t="inlineStr"/>
       <c r="E10" s="21" t="inlineStr"/>
       <c r="F10" s="21" t="inlineStr"/>
@@ -7587,7 +7596,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 $9710万
@@ -7595,7 +7604,7 @@
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 $9029万
@@ -7614,7 +7623,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 $10934万
@@ -7622,7 +7631,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 $7773万
@@ -7641,7 +7650,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $5043万
@@ -7649,7 +7658,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5934万
@@ -7657,7 +7666,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4423万
@@ -7675,7 +7684,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $5094万
@@ -7683,7 +7692,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $6874万
@@ -7691,7 +7700,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4882万
@@ -7709,7 +7718,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4939万
@@ -7717,7 +7726,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $6307万
@@ -7725,7 +7734,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $5270万
@@ -7743,7 +7752,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4507万
@@ -7751,7 +7760,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5083万
@@ -7759,7 +7768,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4363万
@@ -7777,7 +7786,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4409万
@@ -7785,7 +7794,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5058万
@@ -7793,7 +7802,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4924万
@@ -7811,7 +7820,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4394万
@@ -7819,7 +7828,7 @@
 (26年-03月-04日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5102万
@@ -7827,7 +7836,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4832万
@@ -7845,7 +7854,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4322万
@@ -7853,7 +7862,7 @@
 (26年-02月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5134万
@@ -7861,7 +7870,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4383万
@@ -7879,7 +7888,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4296万
@@ -7887,7 +7896,7 @@
 (26年-02月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $4962万
@@ -7895,7 +7904,7 @@
 (26年-02月-06日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4261万
@@ -7913,7 +7922,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4425万
@@ -7921,7 +7930,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5102万
@@ -7929,7 +7938,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4231万
@@ -7947,7 +7956,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2559万
@@ -7955,7 +7964,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1993万
@@ -7963,7 +7972,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $2381万
@@ -7971,7 +7980,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2413万
@@ -7979,7 +7988,7 @@
 (26年-03月-23日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1490万
@@ -7987,7 +7996,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1486万
@@ -8002,7 +8011,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2426万
@@ -8010,7 +8019,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1955万
@@ -8018,7 +8027,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1930万
@@ -8026,7 +8035,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2350万
@@ -8034,7 +8043,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1467万
@@ -8042,7 +8051,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1459万
@@ -8057,7 +8066,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2264万
@@ -8065,7 +8074,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1864万
@@ -8073,7 +8082,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1847万
@@ -8081,7 +8090,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2197万
@@ -8089,7 +8098,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1368万
@@ -8097,7 +8106,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1376万
@@ -8112,7 +8121,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2203万
@@ -8120,7 +8129,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1840万
@@ -8128,7 +8137,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1828万
@@ -8136,7 +8145,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2178万
@@ -8144,7 +8153,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1360万
@@ -8152,7 +8161,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1368万
@@ -8167,7 +8176,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2165万
@@ -8175,7 +8184,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1809万
@@ -8183,7 +8192,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1792万
@@ -8191,7 +8200,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2134万
@@ -8199,7 +8208,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1315万
@@ -8207,7 +8216,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1319万
@@ -8222,7 +8231,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2165万
@@ -8230,7 +8239,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1814万
@@ -8238,7 +8247,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1780万
@@ -8246,7 +8255,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2140万
@@ -8254,7 +8263,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1292万
@@ -8262,7 +8271,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1303万
@@ -8277,7 +8286,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2153万
@@ -8285,7 +8294,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1804万
@@ -8293,7 +8302,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1792万
@@ -8301,7 +8310,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2127万
@@ -8309,7 +8318,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1349万
@@ -8317,7 +8326,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1357万
@@ -8332,7 +8341,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2146万
@@ -8340,7 +8349,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1799万
@@ -8348,7 +8357,7 @@
 (26年-03月-18日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1782万
@@ -8356,7 +8365,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2121万
@@ -8364,7 +8373,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1264万
@@ -8372,7 +8381,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1281万
@@ -8387,7 +8396,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2134万
@@ -8395,7 +8404,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1794万
@@ -8403,7 +8412,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1772万
@@ -8411,7 +8420,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2108万
@@ -8419,7 +8428,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1250万
@@ -8427,7 +8436,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1258万
@@ -8442,7 +8451,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 1055呎 (3房)
 $4716万
@@ -8450,7 +8459,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 509呎 (2房)
 $1822万
@@ -8458,7 +8467,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 510呎 (2房)
 $1800万
@@ -8466,7 +8475,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 1055呎 (3房)
 $4610万

--- a/web/files/港岛-半山-雅盈峰.xlsx
+++ b/web/files/港岛-半山-雅盈峰.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,12 +121,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -272,10 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -907,23 +898,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>94434000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>75306</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -932,12 +919,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -947,7 +934,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7368,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7391,7 +7378,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7499,9 +7486,9 @@
       <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
-招标单位
--
-(在售)</t>
+$9443万
+$75,306/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7542,7 +7529,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 $10323万
@@ -7550,7 +7537,7 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 $7499万
@@ -7596,7 +7583,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 $9710万
@@ -7604,7 +7591,7 @@
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 $9029万
@@ -7623,7 +7610,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1608呎 (4+房)
 $10934万
@@ -7631,7 +7618,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1254呎 (3房)
 $7773万
@@ -7650,7 +7637,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $5043万
@@ -7658,7 +7645,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5934万
@@ -7666,7 +7653,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4423万
@@ -7684,7 +7671,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $5094万
@@ -7692,7 +7679,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $6874万
@@ -7700,7 +7687,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4882万
@@ -7718,7 +7705,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4939万
@@ -7726,7 +7713,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $6307万
@@ -7734,7 +7721,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $5270万
@@ -7752,7 +7739,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4507万
@@ -7760,7 +7747,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5083万
@@ -7768,7 +7755,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4363万
@@ -7786,7 +7773,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4409万
@@ -7794,7 +7781,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5058万
@@ -7802,7 +7789,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4924万
@@ -7820,7 +7807,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4394万
@@ -7828,7 +7815,7 @@
 (26年-03月-04日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5102万
@@ -7836,7 +7823,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4832万
@@ -7854,7 +7841,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4322万
@@ -7862,7 +7849,7 @@
 (26年-02月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5134万
@@ -7870,7 +7857,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4383万
@@ -7888,7 +7875,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4296万
@@ -7896,7 +7883,7 @@
 (26年-02月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $4962万
@@ -7904,7 +7891,7 @@
 (26年-02月-06日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4261万
@@ -7922,7 +7909,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 1029呎 (3房)
 $4425万
@@ -7930,7 +7917,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1074呎 (3房)
 $5102万
@@ -7938,7 +7925,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 1017呎 (3房)
 $4231万
@@ -7956,7 +7943,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2559万
@@ -7964,7 +7951,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1993万
@@ -7972,7 +7959,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $2381万
@@ -7980,7 +7967,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2413万
@@ -7988,7 +7975,7 @@
 (26年-03月-23日)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1490万
@@ -7996,7 +7983,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1486万
@@ -8011,7 +7998,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2426万
@@ -8019,7 +8006,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1955万
@@ -8027,7 +8014,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1930万
@@ -8035,7 +8022,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2350万
@@ -8043,7 +8030,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1467万
@@ -8051,7 +8038,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1459万
@@ -8066,7 +8053,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2264万
@@ -8074,7 +8061,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1864万
@@ -8082,7 +8069,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1847万
@@ -8090,7 +8077,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2197万
@@ -8098,7 +8085,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1368万
@@ -8106,7 +8093,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1376万
@@ -8121,7 +8108,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2203万
@@ -8129,7 +8116,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1840万
@@ -8137,7 +8124,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1828万
@@ -8145,7 +8132,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2178万
@@ -8153,7 +8140,7 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1360万
@@ -8161,7 +8148,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1368万
@@ -8176,7 +8163,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2165万
@@ -8184,7 +8171,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1809万
@@ -8192,7 +8179,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1792万
@@ -8200,7 +8187,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2134万
@@ -8208,7 +8195,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1315万
@@ -8216,7 +8203,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1319万
@@ -8231,7 +8218,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2165万
@@ -8239,7 +8226,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1814万
@@ -8247,7 +8234,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1780万
@@ -8255,7 +8242,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2140万
@@ -8263,7 +8250,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1292万
@@ -8271,7 +8258,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1303万
@@ -8286,7 +8273,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2153万
@@ -8294,7 +8281,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1804万
@@ -8302,7 +8289,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1792万
@@ -8310,7 +8297,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2127万
@@ -8318,7 +8305,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1349万
@@ -8326,7 +8313,7 @@
 (26年-03月-17日)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1357万
@@ -8341,7 +8328,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2146万
@@ -8349,7 +8336,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1799万
@@ -8357,7 +8344,7 @@
 (26年-03月-18日)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1782万
@@ -8365,7 +8352,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2121万
@@ -8373,7 +8360,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1264万
@@ -8381,7 +8368,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1281万
@@ -8396,7 +8383,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 635呎 (2房)
 $2134万
@@ -8404,7 +8391,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 511呎 (2房)
 $1794万
@@ -8412,7 +8399,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 512呎 (2房)
 $1772万
@@ -8420,7 +8407,7 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 635呎 (2房)
 $2108万
@@ -8428,7 +8415,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 380呎 (1房)
 $1250万
@@ -8436,7 +8423,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>F | 380呎 (1房)
 $1258万
@@ -8451,7 +8438,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 1055呎 (3房)
 $4716万
@@ -8459,7 +8446,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 509呎 (2房)
 $1822万
@@ -8467,7 +8454,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 510呎 (2房)
 $1800万
@@ -8475,7 +8462,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 1055呎 (3房)
 $4610万

--- a/web/files/港岛-半山-雅盈峰.xlsx
+++ b/web/files/港岛-半山-雅盈峰.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -7488,7 +7488,7 @@
           <t>B | 1254呎 (3房)
 $9443万
 $75,306/呎
-(26年-09月-28日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
